--- a/public/resumen_modelos.xlsx
+++ b/public/resumen_modelos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistral-saba-24b</t>
+          <t>llama-4-scout-17b-16e-instruct</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -634,10 +634,10 @@
         <v>10485</v>
       </c>
       <c r="E6" t="n">
-        <v>74.14</v>
+        <v>82.03</v>
       </c>
       <c r="F6" t="n">
-        <v>65.53</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,34 +653,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>mistral-saba-24b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Direct Prompt</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10485</v>
+      </c>
+      <c r="E7" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>o4-mini</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Direct Prompt</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1645</v>
-      </c>
-      <c r="E7" t="n">
-        <v>39.82</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D8" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E8" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
